--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110011</v>
+        <v>110013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barkhult, 1,0 km SSV, Sk</t>
+          <t>Barkhult, 1,0 km SSV, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -741,6 +741,11 @@
       <c r="W2" t="inlineStr">
         <is>
           <t>Hörja</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Hlm-0560</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110013</v>
+        <v>110020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110020</v>
+        <v>110029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110029</v>
+        <v>110037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110055</v>
+        <v>110065</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110065</v>
+        <v>110078</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41120-2019 artfynd.xlsx
+++ b/artfynd/A 41120-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122019939</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>110083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
